--- a/artfynd/A 25837-2025 artfynd.xlsx
+++ b/artfynd/A 25837-2025 artfynd.xlsx
@@ -925,42 +925,42 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131106823</v>
+        <v>131106812</v>
       </c>
       <c r="B4" t="n">
-        <v>80348</v>
+        <v>99013</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -969,10 +969,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>600504</v>
+        <v>600509</v>
       </c>
       <c r="R4" t="n">
-        <v>6974579</v>
+        <v>6974463</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -999,7 +999,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2025_0354</t>
+          <t>2025_0365</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1050,42 +1050,42 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131106812</v>
+        <v>131106823</v>
       </c>
       <c r="B5" t="n">
-        <v>99013</v>
+        <v>80348</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1094,10 +1094,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>600509</v>
+        <v>600504</v>
       </c>
       <c r="R5" t="n">
-        <v>6974463</v>
+        <v>6974579</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1124,7 +1124,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2025_0365</t>
+          <t>2025_0354</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1175,10 +1175,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131106815</v>
+        <v>131106822</v>
       </c>
       <c r="B6" t="n">
-        <v>99036</v>
+        <v>98930</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1186,26 +1186,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221952</v>
+        <v>219790</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1219,10 +1219,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>600490</v>
+        <v>600502</v>
       </c>
       <c r="R6" t="n">
-        <v>6974472</v>
+        <v>6974543</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1249,7 +1249,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2025_0362</t>
+          <t>2025_0355</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1269,7 +1269,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1289,7 +1289,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>David Isaksson, Anders Forsberg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1300,7 +1300,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131106813</v>
+        <v>131106815</v>
       </c>
       <c r="B7" t="n">
         <v>99036</v>
@@ -1330,7 +1330,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1344,10 +1344,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>600498</v>
+        <v>600490</v>
       </c>
       <c r="R7" t="n">
-        <v>6974468</v>
+        <v>6974472</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1374,7 +1374,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2025_0364</t>
+          <t>2025_0362</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1394,7 +1394,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>David Isaksson, Anders Forsberg</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1425,42 +1425,42 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131106821</v>
+        <v>131106813</v>
       </c>
       <c r="B8" t="n">
-        <v>80348</v>
+        <v>99036</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1469,10 +1469,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>600501</v>
+        <v>600498</v>
       </c>
       <c r="R8" t="n">
-        <v>6974538</v>
+        <v>6974468</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2025_0356</t>
+          <t>2025_0364</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1519,12 +1519,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:52</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>På sälglåga</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1555,32 +1550,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131106822</v>
+        <v>131106821</v>
       </c>
       <c r="B9" t="n">
-        <v>98930</v>
+        <v>80348</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219790</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1590,7 +1585,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1599,10 +1594,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>600502</v>
+        <v>600501</v>
       </c>
       <c r="R9" t="n">
-        <v>6974543</v>
+        <v>6974538</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1629,7 +1624,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>2025_0355</t>
+          <t>2025_0356</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1639,7 +1634,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1649,7 +1644,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:52</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På sälglåga</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 25837-2025 artfynd.xlsx
+++ b/artfynd/A 25837-2025 artfynd.xlsx
@@ -925,42 +925,42 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131106812</v>
+        <v>131106823</v>
       </c>
       <c r="B4" t="n">
-        <v>99013</v>
+        <v>80348</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -969,10 +969,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>600509</v>
+        <v>600504</v>
       </c>
       <c r="R4" t="n">
-        <v>6974463</v>
+        <v>6974579</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -999,7 +999,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2025_0365</t>
+          <t>2025_0354</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1050,42 +1050,42 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131106823</v>
+        <v>131106812</v>
       </c>
       <c r="B5" t="n">
-        <v>80348</v>
+        <v>99013</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1094,10 +1094,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>600504</v>
+        <v>600509</v>
       </c>
       <c r="R5" t="n">
-        <v>6974579</v>
+        <v>6974463</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1124,7 +1124,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2025_0354</t>
+          <t>2025_0365</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1175,32 +1175,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131106822</v>
+        <v>131106821</v>
       </c>
       <c r="B6" t="n">
-        <v>98930</v>
+        <v>80348</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219790</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1210,7 +1210,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1219,10 +1219,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>600502</v>
+        <v>600501</v>
       </c>
       <c r="R6" t="n">
-        <v>6974543</v>
+        <v>6974538</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1249,7 +1249,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2025_0355</t>
+          <t>2025_0356</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1269,7 +1269,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:52</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På sälglåga</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1550,32 +1555,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131106821</v>
+        <v>131106822</v>
       </c>
       <c r="B9" t="n">
-        <v>80348</v>
+        <v>98930</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>219790</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1585,7 +1590,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1594,10 +1599,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>600501</v>
+        <v>600502</v>
       </c>
       <c r="R9" t="n">
-        <v>6974538</v>
+        <v>6974543</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1624,7 +1629,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>2025_0356</t>
+          <t>2025_0355</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1634,7 +1639,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1644,12 +1649,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:52</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>På sälglåga</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1925,42 +1925,42 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131106814</v>
+        <v>131106817</v>
       </c>
       <c r="B12" t="n">
-        <v>80348</v>
+        <v>99013</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1969,10 +1969,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>600517</v>
+        <v>600479</v>
       </c>
       <c r="R12" t="n">
-        <v>6974472</v>
+        <v>6974506</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1999,7 +1999,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>2025_0363</t>
+          <t>2025_0360</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -2009,7 +2009,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2019,7 +2019,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2050,42 +2050,42 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131106817</v>
+        <v>131106814</v>
       </c>
       <c r="B13" t="n">
-        <v>99013</v>
+        <v>80348</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2094,10 +2094,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>600479</v>
+        <v>600517</v>
       </c>
       <c r="R13" t="n">
-        <v>6974506</v>
+        <v>6974472</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2124,7 +2124,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>2025_0360</t>
+          <t>2025_0363</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -2134,7 +2134,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2144,7 +2144,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 25837-2025 artfynd.xlsx
+++ b/artfynd/A 25837-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131106816</v>
       </c>
       <c r="B2" t="n">
-        <v>98917</v>
+        <v>98918</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>David Isaksson, Liam Martin</t>
+          <t>Liam Martin, David Isaksson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -803,7 +803,7 @@
         <v>131106818</v>
       </c>
       <c r="B3" t="n">
-        <v>98930</v>
+        <v>98931</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>David Isaksson, Anders Forsberg</t>
+          <t>Anders Forsberg, David Isaksson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -928,7 +928,7 @@
         <v>131106823</v>
       </c>
       <c r="B4" t="n">
-        <v>80348</v>
+        <v>80349</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         <v>131106812</v>
       </c>
       <c r="B5" t="n">
-        <v>99013</v>
+        <v>99014</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         <v>131106821</v>
       </c>
       <c r="B6" t="n">
-        <v>80348</v>
+        <v>80349</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>David Isaksson, Anders Forsberg</t>
+          <t>Anders Forsberg, David Isaksson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1308,7 +1308,7 @@
         <v>131106815</v>
       </c>
       <c r="B7" t="n">
-        <v>99036</v>
+        <v>99037</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>131106813</v>
       </c>
       <c r="B8" t="n">
-        <v>99036</v>
+        <v>99037</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>David Isaksson, Anders Forsberg</t>
+          <t>Anders Forsberg, David Isaksson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1558,7 +1558,7 @@
         <v>131106822</v>
       </c>
       <c r="B9" t="n">
-        <v>98930</v>
+        <v>98931</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1669,7 +1669,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>David Isaksson, Anders Forsberg</t>
+          <t>Anders Forsberg, David Isaksson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>David Isaksson, Anders Forsberg</t>
+          <t>Anders Forsberg, David Isaksson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1803,7 +1803,7 @@
         <v>131106819</v>
       </c>
       <c r="B11" t="n">
-        <v>99036</v>
+        <v>99037</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1914,7 +1914,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>David Isaksson, Anders Forsberg</t>
+          <t>Anders Forsberg, David Isaksson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1928,7 +1928,7 @@
         <v>131106817</v>
       </c>
       <c r="B12" t="n">
-        <v>99013</v>
+        <v>99014</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
         <v>131106814</v>
       </c>
       <c r="B13" t="n">
-        <v>80348</v>
+        <v>80349</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 25837-2025 artfynd.xlsx
+++ b/artfynd/A 25837-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Liam Martin, David Isaksson</t>
+          <t>David Isaksson, Liam Martin</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -914,7 +914,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anders Forsberg, David Isaksson</t>
+          <t>David Isaksson, Anders Forsberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -1175,42 +1175,42 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131106821</v>
+        <v>131106815</v>
       </c>
       <c r="B6" t="n">
-        <v>80349</v>
+        <v>99037</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1219,10 +1219,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>600501</v>
+        <v>600490</v>
       </c>
       <c r="R6" t="n">
-        <v>6974538</v>
+        <v>6974472</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1249,7 +1249,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2025_0356</t>
+          <t>2025_0362</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1269,12 +1269,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:52</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På sälglåga</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1294,7 +1289,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anders Forsberg, David Isaksson</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1305,7 +1300,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131106815</v>
+        <v>131106813</v>
       </c>
       <c r="B7" t="n">
         <v>99037</v>
@@ -1335,7 +1330,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1349,10 +1344,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>600490</v>
+        <v>600498</v>
       </c>
       <c r="R7" t="n">
-        <v>6974472</v>
+        <v>6974468</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1379,7 +1374,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2025_0362</t>
+          <t>2025_0364</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1389,7 +1384,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1399,7 +1394,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1419,7 +1414,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>David Isaksson, Anders Forsberg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1430,42 +1425,42 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131106813</v>
+        <v>131106821</v>
       </c>
       <c r="B8" t="n">
-        <v>99037</v>
+        <v>80349</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1474,10 +1469,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>600498</v>
+        <v>600501</v>
       </c>
       <c r="R8" t="n">
-        <v>6974468</v>
+        <v>6974538</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1504,7 +1499,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2025_0364</t>
+          <t>2025_0356</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1514,7 +1509,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1524,7 +1519,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>12:52</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På sälglåga</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anders Forsberg, David Isaksson</t>
+          <t>David Isaksson, Anders Forsberg</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1669,7 +1669,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anders Forsberg, David Isaksson</t>
+          <t>David Isaksson, Anders Forsberg</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anders Forsberg, David Isaksson</t>
+          <t>David Isaksson, Anders Forsberg</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anders Forsberg, David Isaksson</t>
+          <t>David Isaksson, Anders Forsberg</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1925,42 +1925,42 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131106817</v>
+        <v>131106814</v>
       </c>
       <c r="B12" t="n">
-        <v>99014</v>
+        <v>80349</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1969,10 +1969,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>600479</v>
+        <v>600517</v>
       </c>
       <c r="R12" t="n">
-        <v>6974506</v>
+        <v>6974472</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1999,7 +1999,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>2025_0360</t>
+          <t>2025_0363</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -2009,7 +2009,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2019,7 +2019,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2050,42 +2050,42 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131106814</v>
+        <v>131106817</v>
       </c>
       <c r="B13" t="n">
-        <v>80349</v>
+        <v>99014</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2094,10 +2094,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>600517</v>
+        <v>600479</v>
       </c>
       <c r="R13" t="n">
-        <v>6974472</v>
+        <v>6974506</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2124,7 +2124,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>2025_0363</t>
+          <t>2025_0360</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -2134,7 +2134,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2144,7 +2144,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 25837-2025 artfynd.xlsx
+++ b/artfynd/A 25837-2025 artfynd.xlsx
@@ -1175,42 +1175,42 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131106815</v>
+        <v>131106821</v>
       </c>
       <c r="B6" t="n">
-        <v>99037</v>
+        <v>80349</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1219,10 +1219,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>600490</v>
+        <v>600501</v>
       </c>
       <c r="R6" t="n">
-        <v>6974472</v>
+        <v>6974538</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1249,7 +1249,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2025_0362</t>
+          <t>2025_0356</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1269,7 +1269,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>12:52</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På sälglåga</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1289,7 +1294,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>David Isaksson, Anders Forsberg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1300,10 +1305,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131106813</v>
+        <v>131106822</v>
       </c>
       <c r="B7" t="n">
-        <v>99037</v>
+        <v>98931</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1311,26 +1316,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221952</v>
+        <v>219790</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1344,10 +1349,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>600498</v>
+        <v>600502</v>
       </c>
       <c r="R7" t="n">
-        <v>6974468</v>
+        <v>6974543</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1374,7 +1379,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2025_0364</t>
+          <t>2025_0355</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1384,7 +1389,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1394,7 +1399,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1425,42 +1430,42 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131106821</v>
+        <v>131106815</v>
       </c>
       <c r="B8" t="n">
-        <v>80349</v>
+        <v>99037</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1469,10 +1474,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>600501</v>
+        <v>600490</v>
       </c>
       <c r="R8" t="n">
-        <v>6974538</v>
+        <v>6974472</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1499,7 +1504,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2025_0356</t>
+          <t>2025_0362</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1509,7 +1514,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1519,12 +1524,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:52</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>På sälglåga</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>David Isaksson, Anders Forsberg</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1555,10 +1555,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131106822</v>
+        <v>131106813</v>
       </c>
       <c r="B9" t="n">
-        <v>98931</v>
+        <v>99037</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1566,26 +1566,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219790</v>
+        <v>221952</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1599,10 +1599,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>600502</v>
+        <v>600498</v>
       </c>
       <c r="R9" t="n">
-        <v>6974543</v>
+        <v>6974468</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>2025_0355</t>
+          <t>2025_0364</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1639,7 +1639,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1649,7 +1649,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 25837-2025 artfynd.xlsx
+++ b/artfynd/A 25837-2025 artfynd.xlsx
@@ -925,42 +925,42 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131106823</v>
+        <v>131106812</v>
       </c>
       <c r="B4" t="n">
-        <v>80349</v>
+        <v>99014</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -969,10 +969,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>600504</v>
+        <v>600509</v>
       </c>
       <c r="R4" t="n">
-        <v>6974579</v>
+        <v>6974463</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -999,7 +999,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2025_0354</t>
+          <t>2025_0365</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1050,42 +1050,42 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131106812</v>
+        <v>131106823</v>
       </c>
       <c r="B5" t="n">
-        <v>99014</v>
+        <v>80349</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1094,10 +1094,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>600509</v>
+        <v>600504</v>
       </c>
       <c r="R5" t="n">
-        <v>6974463</v>
+        <v>6974579</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1124,7 +1124,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2025_0365</t>
+          <t>2025_0354</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 25837-2025 artfynd.xlsx
+++ b/artfynd/A 25837-2025 artfynd.xlsx
@@ -925,42 +925,42 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131106812</v>
+        <v>131106823</v>
       </c>
       <c r="B4" t="n">
-        <v>99014</v>
+        <v>80349</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -969,10 +969,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>600509</v>
+        <v>600504</v>
       </c>
       <c r="R4" t="n">
-        <v>6974463</v>
+        <v>6974579</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -999,7 +999,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2025_0365</t>
+          <t>2025_0354</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1050,42 +1050,42 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131106823</v>
+        <v>131106812</v>
       </c>
       <c r="B5" t="n">
-        <v>80349</v>
+        <v>99014</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1094,10 +1094,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>600504</v>
+        <v>600509</v>
       </c>
       <c r="R5" t="n">
-        <v>6974579</v>
+        <v>6974463</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1124,7 +1124,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2025_0354</t>
+          <t>2025_0365</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1925,42 +1925,42 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131106814</v>
+        <v>131106817</v>
       </c>
       <c r="B12" t="n">
-        <v>80349</v>
+        <v>99014</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1969,10 +1969,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>600517</v>
+        <v>600479</v>
       </c>
       <c r="R12" t="n">
-        <v>6974472</v>
+        <v>6974506</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1999,7 +1999,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>2025_0363</t>
+          <t>2025_0360</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -2009,7 +2009,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2019,7 +2019,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2050,42 +2050,42 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131106817</v>
+        <v>131106814</v>
       </c>
       <c r="B13" t="n">
-        <v>99014</v>
+        <v>80349</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2094,10 +2094,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>600479</v>
+        <v>600517</v>
       </c>
       <c r="R13" t="n">
-        <v>6974506</v>
+        <v>6974472</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2124,7 +2124,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>2025_0360</t>
+          <t>2025_0363</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -2134,7 +2134,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2144,7 +2144,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 25837-2025 artfynd.xlsx
+++ b/artfynd/A 25837-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131106816</v>
       </c>
       <c r="B2" t="n">
-        <v>98918</v>
+        <v>98919</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>131106818</v>
       </c>
       <c r="B3" t="n">
-        <v>98931</v>
+        <v>98932</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -928,7 +928,7 @@
         <v>131106823</v>
       </c>
       <c r="B4" t="n">
-        <v>80349</v>
+        <v>80350</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         <v>131106812</v>
       </c>
       <c r="B5" t="n">
-        <v>99014</v>
+        <v>99015</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         <v>131106821</v>
       </c>
       <c r="B6" t="n">
-        <v>80349</v>
+        <v>80350</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1305,10 +1305,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131106822</v>
+        <v>131106815</v>
       </c>
       <c r="B7" t="n">
-        <v>98931</v>
+        <v>99038</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1316,26 +1316,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219790</v>
+        <v>221952</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1349,10 +1349,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>600502</v>
+        <v>600490</v>
       </c>
       <c r="R7" t="n">
-        <v>6974543</v>
+        <v>6974472</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2025_0355</t>
+          <t>2025_0362</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1399,7 +1399,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>David Isaksson, Anders Forsberg</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1430,10 +1430,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131106815</v>
+        <v>131106813</v>
       </c>
       <c r="B8" t="n">
-        <v>99037</v>
+        <v>99038</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1474,10 +1474,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>600490</v>
+        <v>600498</v>
       </c>
       <c r="R8" t="n">
-        <v>6974472</v>
+        <v>6974468</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2025_0362</t>
+          <t>2025_0364</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1514,7 +1514,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>David Isaksson, Anders Forsberg</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1555,10 +1555,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131106813</v>
+        <v>131106822</v>
       </c>
       <c r="B9" t="n">
-        <v>99037</v>
+        <v>98932</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1566,26 +1566,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221952</v>
+        <v>219790</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1599,10 +1599,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>600498</v>
+        <v>600502</v>
       </c>
       <c r="R9" t="n">
-        <v>6974468</v>
+        <v>6974543</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>2025_0364</t>
+          <t>2025_0355</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1639,7 +1639,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1649,7 +1649,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1683,7 +1683,7 @@
         <v>131106820</v>
       </c>
       <c r="B10" t="n">
-        <v>58316</v>
+        <v>58317</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>131106819</v>
       </c>
       <c r="B11" t="n">
-        <v>99037</v>
+        <v>99038</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1925,42 +1925,42 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131106817</v>
+        <v>131106814</v>
       </c>
       <c r="B12" t="n">
-        <v>99014</v>
+        <v>80350</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1969,10 +1969,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>600479</v>
+        <v>600517</v>
       </c>
       <c r="R12" t="n">
-        <v>6974506</v>
+        <v>6974472</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1999,7 +1999,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>2025_0360</t>
+          <t>2025_0363</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -2009,7 +2009,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2019,7 +2019,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2050,42 +2050,42 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131106814</v>
+        <v>131106817</v>
       </c>
       <c r="B13" t="n">
-        <v>80349</v>
+        <v>99015</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2094,10 +2094,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>600517</v>
+        <v>600479</v>
       </c>
       <c r="R13" t="n">
-        <v>6974472</v>
+        <v>6974506</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2124,7 +2124,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>2025_0363</t>
+          <t>2025_0360</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -2134,7 +2134,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2144,7 +2144,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 25837-2025 artfynd.xlsx
+++ b/artfynd/A 25837-2025 artfynd.xlsx
@@ -925,42 +925,42 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131106823</v>
+        <v>131106812</v>
       </c>
       <c r="B4" t="n">
-        <v>80350</v>
+        <v>99015</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -969,10 +969,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>600504</v>
+        <v>600509</v>
       </c>
       <c r="R4" t="n">
-        <v>6974579</v>
+        <v>6974463</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -999,7 +999,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2025_0354</t>
+          <t>2025_0365</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1050,42 +1050,42 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131106812</v>
+        <v>131106823</v>
       </c>
       <c r="B5" t="n">
-        <v>99015</v>
+        <v>80350</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1094,10 +1094,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>600509</v>
+        <v>600504</v>
       </c>
       <c r="R5" t="n">
-        <v>6974463</v>
+        <v>6974579</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1124,7 +1124,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2025_0365</t>
+          <t>2025_0354</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 25837-2025 artfynd.xlsx
+++ b/artfynd/A 25837-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131106816</v>
       </c>
       <c r="B2" t="n">
-        <v>98919</v>
+        <v>98922</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>131106818</v>
       </c>
       <c r="B3" t="n">
-        <v>98932</v>
+        <v>98935</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,42 +925,42 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131106812</v>
+        <v>131106823</v>
       </c>
       <c r="B4" t="n">
-        <v>99015</v>
+        <v>80350</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -969,10 +969,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>600509</v>
+        <v>600504</v>
       </c>
       <c r="R4" t="n">
-        <v>6974463</v>
+        <v>6974579</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -999,7 +999,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2025_0365</t>
+          <t>2025_0354</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1050,42 +1050,42 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131106823</v>
+        <v>131106812</v>
       </c>
       <c r="B5" t="n">
-        <v>80350</v>
+        <v>99018</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1094,10 +1094,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>600504</v>
+        <v>600509</v>
       </c>
       <c r="R5" t="n">
-        <v>6974579</v>
+        <v>6974463</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1124,7 +1124,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2025_0354</t>
+          <t>2025_0365</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1175,42 +1175,42 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131106821</v>
+        <v>131106815</v>
       </c>
       <c r="B6" t="n">
-        <v>80350</v>
+        <v>99041</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1219,10 +1219,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>600501</v>
+        <v>600490</v>
       </c>
       <c r="R6" t="n">
-        <v>6974538</v>
+        <v>6974472</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1249,7 +1249,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2025_0356</t>
+          <t>2025_0362</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1269,12 +1269,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:52</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På sälglåga</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1294,7 +1289,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>David Isaksson, Anders Forsberg</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1305,10 +1300,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131106815</v>
+        <v>131106813</v>
       </c>
       <c r="B7" t="n">
-        <v>99038</v>
+        <v>99041</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1335,7 +1330,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1349,10 +1344,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>600490</v>
+        <v>600498</v>
       </c>
       <c r="R7" t="n">
-        <v>6974472</v>
+        <v>6974468</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1379,7 +1374,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2025_0362</t>
+          <t>2025_0364</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1389,7 +1384,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1399,7 +1394,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1419,7 +1414,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>David Isaksson, Anders Forsberg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1430,42 +1425,42 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131106813</v>
+        <v>131106821</v>
       </c>
       <c r="B8" t="n">
-        <v>99038</v>
+        <v>80350</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1474,10 +1469,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>600498</v>
+        <v>600501</v>
       </c>
       <c r="R8" t="n">
-        <v>6974468</v>
+        <v>6974538</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1504,7 +1499,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2025_0364</t>
+          <t>2025_0356</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1514,7 +1509,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1524,7 +1519,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>12:52</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På sälglåga</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1558,7 +1558,7 @@
         <v>131106822</v>
       </c>
       <c r="B9" t="n">
-        <v>98932</v>
+        <v>98935</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>131106819</v>
       </c>
       <c r="B11" t="n">
-        <v>99038</v>
+        <v>99041</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
         <v>131106817</v>
       </c>
       <c r="B13" t="n">
-        <v>99015</v>
+        <v>99018</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 25837-2025 artfynd.xlsx
+++ b/artfynd/A 25837-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131106816</v>
       </c>
       <c r="B2" t="n">
-        <v>98922</v>
+        <v>98923</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>131106818</v>
       </c>
       <c r="B3" t="n">
-        <v>98935</v>
+        <v>98936</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -928,7 +928,7 @@
         <v>131106823</v>
       </c>
       <c r="B4" t="n">
-        <v>80350</v>
+        <v>80351</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         <v>131106812</v>
       </c>
       <c r="B5" t="n">
-        <v>99018</v>
+        <v>99019</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1175,10 +1175,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131106815</v>
+        <v>131106822</v>
       </c>
       <c r="B6" t="n">
-        <v>99041</v>
+        <v>98936</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1186,26 +1186,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221952</v>
+        <v>219790</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1219,10 +1219,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>600490</v>
+        <v>600502</v>
       </c>
       <c r="R6" t="n">
-        <v>6974472</v>
+        <v>6974543</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1249,7 +1249,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2025_0362</t>
+          <t>2025_0355</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1269,7 +1269,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1289,7 +1289,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>David Isaksson, Anders Forsberg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1300,10 +1300,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131106813</v>
+        <v>131106815</v>
       </c>
       <c r="B7" t="n">
-        <v>99041</v>
+        <v>99042</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1344,10 +1344,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>600498</v>
+        <v>600490</v>
       </c>
       <c r="R7" t="n">
-        <v>6974468</v>
+        <v>6974472</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1374,7 +1374,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2025_0364</t>
+          <t>2025_0362</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1394,7 +1394,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>David Isaksson, Anders Forsberg</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1425,42 +1425,42 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131106821</v>
+        <v>131106813</v>
       </c>
       <c r="B8" t="n">
-        <v>80350</v>
+        <v>99042</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1469,10 +1469,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>600501</v>
+        <v>600498</v>
       </c>
       <c r="R8" t="n">
-        <v>6974538</v>
+        <v>6974468</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2025_0356</t>
+          <t>2025_0364</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1519,12 +1519,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:52</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>På sälglåga</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1555,32 +1550,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131106822</v>
+        <v>131106821</v>
       </c>
       <c r="B9" t="n">
-        <v>98935</v>
+        <v>80351</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219790</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1590,7 +1585,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1599,10 +1594,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>600502</v>
+        <v>600501</v>
       </c>
       <c r="R9" t="n">
-        <v>6974543</v>
+        <v>6974538</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1629,7 +1624,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>2025_0355</t>
+          <t>2025_0356</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1639,7 +1634,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1649,7 +1644,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:52</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På sälglåga</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1803,7 +1803,7 @@
         <v>131106819</v>
       </c>
       <c r="B11" t="n">
-        <v>99041</v>
+        <v>99042</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>131106814</v>
       </c>
       <c r="B12" t="n">
-        <v>80350</v>
+        <v>80351</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
         <v>131106817</v>
       </c>
       <c r="B13" t="n">
-        <v>99018</v>
+        <v>99019</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 25837-2025 artfynd.xlsx
+++ b/artfynd/A 25837-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131106816</v>
       </c>
       <c r="B2" t="n">
-        <v>98923</v>
+        <v>98925</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>131106818</v>
       </c>
       <c r="B3" t="n">
-        <v>98936</v>
+        <v>98938</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -928,7 +928,7 @@
         <v>131106823</v>
       </c>
       <c r="B4" t="n">
-        <v>80351</v>
+        <v>80353</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         <v>131106812</v>
       </c>
       <c r="B5" t="n">
-        <v>99019</v>
+        <v>99021</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1175,10 +1175,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131106822</v>
+        <v>131106815</v>
       </c>
       <c r="B6" t="n">
-        <v>98936</v>
+        <v>99044</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1186,26 +1186,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219790</v>
+        <v>221952</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1219,10 +1219,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>600502</v>
+        <v>600490</v>
       </c>
       <c r="R6" t="n">
-        <v>6974543</v>
+        <v>6974472</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1249,7 +1249,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2025_0355</t>
+          <t>2025_0362</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1269,7 +1269,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1289,7 +1289,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>David Isaksson, Anders Forsberg</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1300,10 +1300,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131106815</v>
+        <v>131106813</v>
       </c>
       <c r="B7" t="n">
-        <v>99042</v>
+        <v>99044</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1344,10 +1344,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>600490</v>
+        <v>600498</v>
       </c>
       <c r="R7" t="n">
-        <v>6974472</v>
+        <v>6974468</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1374,7 +1374,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2025_0362</t>
+          <t>2025_0364</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1394,7 +1394,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>David Isaksson, Anders Forsberg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1425,42 +1425,42 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131106813</v>
+        <v>131106821</v>
       </c>
       <c r="B8" t="n">
-        <v>99042</v>
+        <v>80353</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1469,10 +1469,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>600498</v>
+        <v>600501</v>
       </c>
       <c r="R8" t="n">
-        <v>6974468</v>
+        <v>6974538</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2025_0364</t>
+          <t>2025_0356</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1519,7 +1519,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>12:52</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På sälglåga</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1550,32 +1555,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131106821</v>
+        <v>131106822</v>
       </c>
       <c r="B9" t="n">
-        <v>80351</v>
+        <v>98938</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>219790</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1585,7 +1590,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1594,10 +1599,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>600501</v>
+        <v>600502</v>
       </c>
       <c r="R9" t="n">
-        <v>6974538</v>
+        <v>6974543</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1624,7 +1629,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>2025_0356</t>
+          <t>2025_0355</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1634,7 +1639,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1644,12 +1649,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:52</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>På sälglåga</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1683,7 +1683,7 @@
         <v>131106820</v>
       </c>
       <c r="B10" t="n">
-        <v>58317</v>
+        <v>58319</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>131106819</v>
       </c>
       <c r="B11" t="n">
-        <v>99042</v>
+        <v>99044</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>131106814</v>
       </c>
       <c r="B12" t="n">
-        <v>80351</v>
+        <v>80353</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
         <v>131106817</v>
       </c>
       <c r="B13" t="n">
-        <v>99019</v>
+        <v>99021</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 25837-2025 artfynd.xlsx
+++ b/artfynd/A 25837-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131106816</v>
       </c>
       <c r="B2" t="n">
-        <v>98925</v>
+        <v>98926</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>131106818</v>
       </c>
       <c r="B3" t="n">
-        <v>98938</v>
+        <v>98939</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,42 +925,42 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131106823</v>
+        <v>131106812</v>
       </c>
       <c r="B4" t="n">
-        <v>80353</v>
+        <v>99022</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -969,10 +969,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>600504</v>
+        <v>600509</v>
       </c>
       <c r="R4" t="n">
-        <v>6974579</v>
+        <v>6974463</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -999,7 +999,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2025_0354</t>
+          <t>2025_0365</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1050,42 +1050,42 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131106812</v>
+        <v>131106823</v>
       </c>
       <c r="B5" t="n">
-        <v>99021</v>
+        <v>80354</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1094,10 +1094,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>600509</v>
+        <v>600504</v>
       </c>
       <c r="R5" t="n">
-        <v>6974463</v>
+        <v>6974579</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1124,7 +1124,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2025_0365</t>
+          <t>2025_0354</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1178,7 +1178,7 @@
         <v>131106815</v>
       </c>
       <c r="B6" t="n">
-        <v>99044</v>
+        <v>99045</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         <v>131106813</v>
       </c>
       <c r="B7" t="n">
-        <v>99044</v>
+        <v>99045</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         <v>131106821</v>
       </c>
       <c r="B8" t="n">
-        <v>80353</v>
+        <v>80354</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1558,7 +1558,7 @@
         <v>131106822</v>
       </c>
       <c r="B9" t="n">
-        <v>98938</v>
+        <v>98939</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         <v>131106820</v>
       </c>
       <c r="B10" t="n">
-        <v>58319</v>
+        <v>58320</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>131106819</v>
       </c>
       <c r="B11" t="n">
-        <v>99044</v>
+        <v>99045</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>131106814</v>
       </c>
       <c r="B12" t="n">
-        <v>80353</v>
+        <v>80354</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
         <v>131106817</v>
       </c>
       <c r="B13" t="n">
-        <v>99021</v>
+        <v>99022</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 25837-2025 artfynd.xlsx
+++ b/artfynd/A 25837-2025 artfynd.xlsx
@@ -925,42 +925,42 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131106812</v>
+        <v>131106823</v>
       </c>
       <c r="B4" t="n">
-        <v>99022</v>
+        <v>80354</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -969,10 +969,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>600509</v>
+        <v>600504</v>
       </c>
       <c r="R4" t="n">
-        <v>6974463</v>
+        <v>6974579</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -999,7 +999,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2025_0365</t>
+          <t>2025_0354</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1050,42 +1050,42 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131106823</v>
+        <v>131106812</v>
       </c>
       <c r="B5" t="n">
-        <v>80354</v>
+        <v>99022</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1094,10 +1094,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>600504</v>
+        <v>600509</v>
       </c>
       <c r="R5" t="n">
-        <v>6974579</v>
+        <v>6974463</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1124,7 +1124,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2025_0354</t>
+          <t>2025_0365</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1175,42 +1175,42 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131106815</v>
+        <v>131106821</v>
       </c>
       <c r="B6" t="n">
-        <v>99045</v>
+        <v>80354</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1219,10 +1219,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>600490</v>
+        <v>600501</v>
       </c>
       <c r="R6" t="n">
-        <v>6974472</v>
+        <v>6974538</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1249,7 +1249,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2025_0362</t>
+          <t>2025_0356</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1269,7 +1269,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>12:52</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På sälglåga</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1289,7 +1294,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>David Isaksson, Anders Forsberg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1300,10 +1305,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131106813</v>
+        <v>131106822</v>
       </c>
       <c r="B7" t="n">
-        <v>99045</v>
+        <v>98939</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1311,26 +1316,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221952</v>
+        <v>219790</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1344,10 +1349,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>600498</v>
+        <v>600502</v>
       </c>
       <c r="R7" t="n">
-        <v>6974468</v>
+        <v>6974543</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1374,7 +1379,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2025_0364</t>
+          <t>2025_0355</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1384,7 +1389,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1394,7 +1399,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1425,42 +1430,42 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131106821</v>
+        <v>131106813</v>
       </c>
       <c r="B8" t="n">
-        <v>80354</v>
+        <v>99045</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1469,10 +1474,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>600501</v>
+        <v>600498</v>
       </c>
       <c r="R8" t="n">
-        <v>6974538</v>
+        <v>6974468</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1499,7 +1504,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2025_0356</t>
+          <t>2025_0364</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1509,7 +1514,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1519,12 +1524,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:52</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>På sälglåga</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1555,10 +1555,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131106822</v>
+        <v>131106815</v>
       </c>
       <c r="B9" t="n">
-        <v>98939</v>
+        <v>99045</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1566,26 +1566,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219790</v>
+        <v>221952</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1599,10 +1599,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>600502</v>
+        <v>600490</v>
       </c>
       <c r="R9" t="n">
-        <v>6974543</v>
+        <v>6974472</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>2025_0355</t>
+          <t>2025_0362</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1639,7 +1639,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1649,7 +1649,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1669,7 +1669,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>David Isaksson, Anders Forsberg</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">

--- a/artfynd/A 25837-2025 artfynd.xlsx
+++ b/artfynd/A 25837-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>David Isaksson, Liam Martin</t>
+          <t>Liam Martin, David Isaksson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -914,7 +914,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>David Isaksson, Anders Forsberg</t>
+          <t>Anders Forsberg, David Isaksson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -1175,42 +1175,42 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131106821</v>
+        <v>131106815</v>
       </c>
       <c r="B6" t="n">
-        <v>80354</v>
+        <v>99045</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1219,10 +1219,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>600501</v>
+        <v>600490</v>
       </c>
       <c r="R6" t="n">
-        <v>6974538</v>
+        <v>6974472</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1249,7 +1249,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2025_0356</t>
+          <t>2025_0362</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1269,12 +1269,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:52</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På sälglåga</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1294,7 +1289,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>David Isaksson, Anders Forsberg</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1305,10 +1300,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131106822</v>
+        <v>131106813</v>
       </c>
       <c r="B7" t="n">
-        <v>98939</v>
+        <v>99045</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1316,26 +1311,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219790</v>
+        <v>221952</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1349,10 +1344,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>600502</v>
+        <v>600498</v>
       </c>
       <c r="R7" t="n">
-        <v>6974543</v>
+        <v>6974468</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1379,7 +1374,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2025_0355</t>
+          <t>2025_0364</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1389,7 +1384,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1399,7 +1394,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1419,7 +1414,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>David Isaksson, Anders Forsberg</t>
+          <t>Anders Forsberg, David Isaksson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1430,10 +1425,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131106813</v>
+        <v>131106822</v>
       </c>
       <c r="B8" t="n">
-        <v>99045</v>
+        <v>98939</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1441,26 +1436,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221952</v>
+        <v>219790</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1474,10 +1469,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>600498</v>
+        <v>600502</v>
       </c>
       <c r="R8" t="n">
-        <v>6974468</v>
+        <v>6974543</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1504,7 +1499,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2025_0364</t>
+          <t>2025_0355</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1514,7 +1509,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1524,7 +1519,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1544,7 +1539,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>David Isaksson, Anders Forsberg</t>
+          <t>Anders Forsberg, David Isaksson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1555,42 +1550,42 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131106815</v>
+        <v>131106821</v>
       </c>
       <c r="B9" t="n">
-        <v>99045</v>
+        <v>80354</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1599,10 +1594,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>600490</v>
+        <v>600501</v>
       </c>
       <c r="R9" t="n">
-        <v>6974472</v>
+        <v>6974538</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1629,7 +1624,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>2025_0362</t>
+          <t>2025_0356</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1639,7 +1634,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1649,7 +1644,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>12:52</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På sälglåga</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1669,7 +1669,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Anders Forsberg, David Isaksson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>David Isaksson, Anders Forsberg</t>
+          <t>Anders Forsberg, David Isaksson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>David Isaksson, Anders Forsberg</t>
+          <t>Anders Forsberg, David Isaksson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">

--- a/artfynd/A 25837-2025 artfynd.xlsx
+++ b/artfynd/A 25837-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131106816</v>
       </c>
       <c r="B2" t="n">
-        <v>98926</v>
+        <v>98927</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Liam Martin, David Isaksson</t>
+          <t>David Isaksson, Liam Martin</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -803,7 +803,7 @@
         <v>131106818</v>
       </c>
       <c r="B3" t="n">
-        <v>98939</v>
+        <v>98940</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anders Forsberg, David Isaksson</t>
+          <t>David Isaksson, Anders Forsberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -928,7 +928,7 @@
         <v>131106823</v>
       </c>
       <c r="B4" t="n">
-        <v>80354</v>
+        <v>80355</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         <v>131106812</v>
       </c>
       <c r="B5" t="n">
-        <v>99022</v>
+        <v>99023</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1175,42 +1175,42 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131106815</v>
+        <v>131106821</v>
       </c>
       <c r="B6" t="n">
-        <v>99045</v>
+        <v>80355</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1219,10 +1219,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>600490</v>
+        <v>600501</v>
       </c>
       <c r="R6" t="n">
-        <v>6974472</v>
+        <v>6974538</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1249,7 +1249,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2025_0362</t>
+          <t>2025_0356</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1269,7 +1269,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>12:52</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På sälglåga</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1289,7 +1294,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>David Isaksson, Anders Forsberg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1300,10 +1305,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131106813</v>
+        <v>131106815</v>
       </c>
       <c r="B7" t="n">
-        <v>99045</v>
+        <v>99046</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1330,7 +1335,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1344,10 +1349,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>600498</v>
+        <v>600490</v>
       </c>
       <c r="R7" t="n">
-        <v>6974468</v>
+        <v>6974472</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1374,7 +1379,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2025_0364</t>
+          <t>2025_0362</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1384,7 +1389,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1394,7 +1399,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1414,7 +1419,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anders Forsberg, David Isaksson</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1425,10 +1430,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131106822</v>
+        <v>131106813</v>
       </c>
       <c r="B8" t="n">
-        <v>98939</v>
+        <v>99046</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1436,26 +1441,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219790</v>
+        <v>221952</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1469,10 +1474,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>600502</v>
+        <v>600498</v>
       </c>
       <c r="R8" t="n">
-        <v>6974543</v>
+        <v>6974468</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1499,7 +1504,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2025_0355</t>
+          <t>2025_0364</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1509,7 +1514,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1519,7 +1524,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1539,7 +1544,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anders Forsberg, David Isaksson</t>
+          <t>David Isaksson, Anders Forsberg</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1550,32 +1555,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131106821</v>
+        <v>131106822</v>
       </c>
       <c r="B9" t="n">
-        <v>80354</v>
+        <v>98940</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>219790</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1585,7 +1590,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1594,10 +1599,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>600501</v>
+        <v>600502</v>
       </c>
       <c r="R9" t="n">
-        <v>6974538</v>
+        <v>6974543</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1624,7 +1629,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>2025_0356</t>
+          <t>2025_0355</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1634,7 +1639,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1644,12 +1649,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:52</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>På sälglåga</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1669,7 +1669,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anders Forsberg, David Isaksson</t>
+          <t>David Isaksson, Anders Forsberg</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1683,7 +1683,7 @@
         <v>131106820</v>
       </c>
       <c r="B10" t="n">
-        <v>58320</v>
+        <v>58321</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anders Forsberg, David Isaksson</t>
+          <t>David Isaksson, Anders Forsberg</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1803,7 +1803,7 @@
         <v>131106819</v>
       </c>
       <c r="B11" t="n">
-        <v>99045</v>
+        <v>99046</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1914,7 +1914,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anders Forsberg, David Isaksson</t>
+          <t>David Isaksson, Anders Forsberg</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1928,7 +1928,7 @@
         <v>131106814</v>
       </c>
       <c r="B12" t="n">
-        <v>80354</v>
+        <v>80355</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
         <v>131106817</v>
       </c>
       <c r="B13" t="n">
-        <v>99022</v>
+        <v>99023</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 25837-2025 artfynd.xlsx
+++ b/artfynd/A 25837-2025 artfynd.xlsx
@@ -1175,42 +1175,42 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131106821</v>
+        <v>131106815</v>
       </c>
       <c r="B6" t="n">
-        <v>80355</v>
+        <v>99046</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1219,10 +1219,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>600501</v>
+        <v>600490</v>
       </c>
       <c r="R6" t="n">
-        <v>6974538</v>
+        <v>6974472</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1249,7 +1249,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2025_0356</t>
+          <t>2025_0362</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1269,12 +1269,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:52</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På sälglåga</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1294,7 +1289,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>David Isaksson, Anders Forsberg</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1305,7 +1300,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131106815</v>
+        <v>131106813</v>
       </c>
       <c r="B7" t="n">
         <v>99046</v>
@@ -1335,7 +1330,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1349,10 +1344,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>600490</v>
+        <v>600498</v>
       </c>
       <c r="R7" t="n">
-        <v>6974472</v>
+        <v>6974468</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1379,7 +1374,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2025_0362</t>
+          <t>2025_0364</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1389,7 +1384,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1399,7 +1394,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1419,7 +1414,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>David Isaksson, Anders Forsberg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1430,42 +1425,42 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131106813</v>
+        <v>131106821</v>
       </c>
       <c r="B8" t="n">
-        <v>99046</v>
+        <v>80355</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1474,10 +1469,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>600498</v>
+        <v>600501</v>
       </c>
       <c r="R8" t="n">
-        <v>6974468</v>
+        <v>6974538</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1504,7 +1499,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2025_0364</t>
+          <t>2025_0356</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1514,7 +1509,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1524,7 +1519,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>12:52</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På sälglåga</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 25837-2025 artfynd.xlsx
+++ b/artfynd/A 25837-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131106816</v>
       </c>
       <c r="B2" t="n">
-        <v>98927</v>
+        <v>98930</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>131106818</v>
       </c>
       <c r="B3" t="n">
-        <v>98940</v>
+        <v>98943</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,42 +925,42 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131106823</v>
+        <v>131106812</v>
       </c>
       <c r="B4" t="n">
-        <v>80355</v>
+        <v>99026</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -969,10 +969,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>600504</v>
+        <v>600509</v>
       </c>
       <c r="R4" t="n">
-        <v>6974579</v>
+        <v>6974463</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -999,7 +999,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2025_0354</t>
+          <t>2025_0365</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1050,42 +1050,42 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131106812</v>
+        <v>131106823</v>
       </c>
       <c r="B5" t="n">
-        <v>99023</v>
+        <v>80358</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1094,10 +1094,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>600509</v>
+        <v>600504</v>
       </c>
       <c r="R5" t="n">
-        <v>6974463</v>
+        <v>6974579</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1124,7 +1124,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2025_0365</t>
+          <t>2025_0354</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1175,42 +1175,42 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131106815</v>
+        <v>131106821</v>
       </c>
       <c r="B6" t="n">
-        <v>99046</v>
+        <v>80358</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1219,10 +1219,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>600490</v>
+        <v>600501</v>
       </c>
       <c r="R6" t="n">
-        <v>6974472</v>
+        <v>6974538</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1249,7 +1249,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2025_0362</t>
+          <t>2025_0356</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1269,7 +1269,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>12:52</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På sälglåga</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1289,7 +1294,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>David Isaksson, Anders Forsberg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1300,10 +1305,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131106813</v>
+        <v>131106822</v>
       </c>
       <c r="B7" t="n">
-        <v>99046</v>
+        <v>98943</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1311,26 +1316,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221952</v>
+        <v>219790</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1344,10 +1349,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>600498</v>
+        <v>600502</v>
       </c>
       <c r="R7" t="n">
-        <v>6974468</v>
+        <v>6974543</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1374,7 +1379,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2025_0364</t>
+          <t>2025_0355</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1384,7 +1389,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1394,7 +1399,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1425,42 +1430,42 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131106821</v>
+        <v>131106815</v>
       </c>
       <c r="B8" t="n">
-        <v>80355</v>
+        <v>99049</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1469,10 +1474,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>600501</v>
+        <v>600490</v>
       </c>
       <c r="R8" t="n">
-        <v>6974538</v>
+        <v>6974472</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1499,7 +1504,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2025_0356</t>
+          <t>2025_0362</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1509,7 +1514,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1519,12 +1524,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:52</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>På sälglåga</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>David Isaksson, Anders Forsberg</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1555,10 +1555,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131106822</v>
+        <v>131106813</v>
       </c>
       <c r="B9" t="n">
-        <v>98940</v>
+        <v>99049</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1566,26 +1566,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219790</v>
+        <v>221952</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1599,10 +1599,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>600502</v>
+        <v>600498</v>
       </c>
       <c r="R9" t="n">
-        <v>6974543</v>
+        <v>6974468</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>2025_0355</t>
+          <t>2025_0364</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1639,7 +1639,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1649,7 +1649,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1683,7 +1683,7 @@
         <v>131106820</v>
       </c>
       <c r="B10" t="n">
-        <v>58321</v>
+        <v>58324</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>131106819</v>
       </c>
       <c r="B11" t="n">
-        <v>99046</v>
+        <v>99049</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>131106814</v>
       </c>
       <c r="B12" t="n">
-        <v>80355</v>
+        <v>80358</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
         <v>131106817</v>
       </c>
       <c r="B13" t="n">
-        <v>99023</v>
+        <v>99026</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 25837-2025 artfynd.xlsx
+++ b/artfynd/A 25837-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131106816</v>
       </c>
       <c r="B2" t="n">
-        <v>98930</v>
+        <v>98931</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>131106818</v>
       </c>
       <c r="B3" t="n">
-        <v>98943</v>
+        <v>98944</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -928,7 +928,7 @@
         <v>131106812</v>
       </c>
       <c r="B4" t="n">
-        <v>99026</v>
+        <v>99027</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         <v>131106823</v>
       </c>
       <c r="B5" t="n">
-        <v>80358</v>
+        <v>80359</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         <v>131106821</v>
       </c>
       <c r="B6" t="n">
-        <v>80358</v>
+        <v>80359</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1305,10 +1305,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131106822</v>
+        <v>131106815</v>
       </c>
       <c r="B7" t="n">
-        <v>98943</v>
+        <v>99050</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1316,26 +1316,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219790</v>
+        <v>221952</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1349,10 +1349,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>600502</v>
+        <v>600490</v>
       </c>
       <c r="R7" t="n">
-        <v>6974543</v>
+        <v>6974472</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2025_0355</t>
+          <t>2025_0362</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1399,7 +1399,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>David Isaksson, Anders Forsberg</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1430,10 +1430,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131106815</v>
+        <v>131106813</v>
       </c>
       <c r="B8" t="n">
-        <v>99049</v>
+        <v>99050</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1474,10 +1474,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>600490</v>
+        <v>600498</v>
       </c>
       <c r="R8" t="n">
-        <v>6974472</v>
+        <v>6974468</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2025_0362</t>
+          <t>2025_0364</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1514,7 +1514,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>David Isaksson, Anders Forsberg</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1555,10 +1555,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131106813</v>
+        <v>131106822</v>
       </c>
       <c r="B9" t="n">
-        <v>99049</v>
+        <v>98944</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1566,26 +1566,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221952</v>
+        <v>219790</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1599,10 +1599,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>600498</v>
+        <v>600502</v>
       </c>
       <c r="R9" t="n">
-        <v>6974468</v>
+        <v>6974543</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>2025_0364</t>
+          <t>2025_0355</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1639,7 +1639,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1649,7 +1649,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1683,7 +1683,7 @@
         <v>131106820</v>
       </c>
       <c r="B10" t="n">
-        <v>58324</v>
+        <v>58325</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>131106819</v>
       </c>
       <c r="B11" t="n">
-        <v>99049</v>
+        <v>99050</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>131106814</v>
       </c>
       <c r="B12" t="n">
-        <v>80358</v>
+        <v>80359</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
         <v>131106817</v>
       </c>
       <c r="B13" t="n">
-        <v>99026</v>
+        <v>99027</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 25837-2025 artfynd.xlsx
+++ b/artfynd/A 25837-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,42 +675,42 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131106816</v>
+        <v>131106814</v>
       </c>
       <c r="B2" t="n">
-        <v>98931</v>
+        <v>80432</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220093</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>600481</v>
+        <v>600517</v>
       </c>
       <c r="R2" t="n">
-        <v>6974525</v>
+        <v>6974472</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,7 +749,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2025_0361</t>
+          <t>2025_0363</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,7 +789,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>David Isaksson, Liam Martin</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -800,42 +800,42 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131106818</v>
+        <v>131106821</v>
       </c>
       <c r="B3" t="n">
-        <v>98944</v>
+        <v>80432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219790</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -844,10 +844,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>600479</v>
+        <v>600501</v>
       </c>
       <c r="R3" t="n">
-        <v>6974511</v>
+        <v>6974538</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -874,7 +874,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2025_0359</t>
+          <t>2025_0356</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -884,7 +884,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -894,7 +894,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:52</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På sälglåga</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -925,42 +930,42 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131106812</v>
+        <v>131106823</v>
       </c>
       <c r="B4" t="n">
-        <v>99027</v>
+        <v>80432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -969,10 +974,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>600509</v>
+        <v>600504</v>
       </c>
       <c r="R4" t="n">
-        <v>6974463</v>
+        <v>6974579</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -999,7 +1004,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2025_0365</t>
+          <t>2025_0354</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1009,7 +1014,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1019,7 +1024,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1050,10 +1055,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131106823</v>
+        <v>131106827</v>
       </c>
       <c r="B5" t="n">
-        <v>80359</v>
+        <v>80432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1080,12 +1085,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1094,10 +1099,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>600504</v>
+        <v>600521</v>
       </c>
       <c r="R5" t="n">
-        <v>6974579</v>
+        <v>6974587</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1124,7 +1129,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2025_0354</t>
+          <t>2025_0350</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1134,7 +1139,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1144,7 +1149,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1164,7 +1169,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>David Isaksson, Anders Forsberg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1175,10 +1180,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131106821</v>
+        <v>131106820</v>
       </c>
       <c r="B6" t="n">
-        <v>80359</v>
+        <v>58388</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1186,21 +1191,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>103001</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1208,21 +1213,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Paljack, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>600501</v>
+        <v>600511</v>
       </c>
       <c r="R6" t="n">
-        <v>6974538</v>
+        <v>6974519</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1249,7 +1249,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2025_0356</t>
+          <t>2025_0357</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1269,12 +1269,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:52</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På sälglåga</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1305,10 +1300,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131106815</v>
+        <v>131106818</v>
       </c>
       <c r="B7" t="n">
-        <v>99050</v>
+        <v>99035</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1316,26 +1311,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221952</v>
+        <v>219790</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1349,10 +1344,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>600490</v>
+        <v>600479</v>
       </c>
       <c r="R7" t="n">
-        <v>6974472</v>
+        <v>6974511</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1379,7 +1374,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2025_0362</t>
+          <t>2025_0359</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1389,7 +1384,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1399,7 +1394,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1419,7 +1414,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>David Isaksson, Anders Forsberg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1430,10 +1425,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131106813</v>
+        <v>131106822</v>
       </c>
       <c r="B8" t="n">
-        <v>99050</v>
+        <v>99035</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1441,26 +1436,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221952</v>
+        <v>219790</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1474,10 +1469,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>600498</v>
+        <v>600502</v>
       </c>
       <c r="R8" t="n">
-        <v>6974468</v>
+        <v>6974543</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1504,7 +1499,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2025_0364</t>
+          <t>2025_0355</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1514,7 +1509,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1524,7 +1519,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1555,10 +1550,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131106822</v>
+        <v>131106826</v>
       </c>
       <c r="B9" t="n">
-        <v>98944</v>
+        <v>99035</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1599,10 +1594,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>600502</v>
+        <v>600516</v>
       </c>
       <c r="R9" t="n">
-        <v>6974543</v>
+        <v>6974599</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1629,7 +1624,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>2025_0355</t>
+          <t>2025_0351</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1639,7 +1634,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1649,7 +1644,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1680,37 +1675,42 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131106820</v>
+        <v>131106816</v>
       </c>
       <c r="B10" t="n">
-        <v>58325</v>
+        <v>99022</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103001</v>
+        <v>220093</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1719,10 +1719,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>600511</v>
+        <v>600481</v>
       </c>
       <c r="R10" t="n">
-        <v>6974519</v>
+        <v>6974525</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1749,7 +1749,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>2025_0357</t>
+          <t>2025_0361</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -1759,7 +1759,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>David Isaksson, Anders Forsberg</t>
+          <t>David Isaksson, Liam Martin</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1800,37 +1800,37 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131106819</v>
+        <v>131106812</v>
       </c>
       <c r="B11" t="n">
-        <v>99050</v>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1844,10 +1844,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>600479</v>
+        <v>600509</v>
       </c>
       <c r="R11" t="n">
-        <v>6974504</v>
+        <v>6974463</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>2025_0358</t>
+          <t>2025_0365</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -1884,7 +1884,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>David Isaksson, Anders Forsberg</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1925,42 +1925,42 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131106814</v>
+        <v>131106817</v>
       </c>
       <c r="B12" t="n">
-        <v>80359</v>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1969,10 +1969,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>600517</v>
+        <v>600479</v>
       </c>
       <c r="R12" t="n">
-        <v>6974472</v>
+        <v>6974506</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1999,7 +1999,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>2025_0363</t>
+          <t>2025_0360</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -2009,7 +2009,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2019,7 +2019,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2050,37 +2050,37 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131106817</v>
+        <v>131106813</v>
       </c>
       <c r="B13" t="n">
-        <v>99027</v>
+        <v>99140</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2094,10 +2094,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>600479</v>
+        <v>600498</v>
       </c>
       <c r="R13" t="n">
-        <v>6974506</v>
+        <v>6974468</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2124,7 +2124,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>2025_0360</t>
+          <t>2025_0364</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -2134,7 +2134,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2144,7 +2144,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2164,10 +2164,385 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
+          <t>David Isaksson, Anders Forsberg</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>131106815</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Paljack, Mpd</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>600490</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6974472</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>2025_0362</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-06-24</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-06-24</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
           <t>David Isaksson</t>
         </is>
       </c>
-      <c r="AY13" t="inlineStr">
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>131106819</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Paljack, Mpd</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>600479</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6974504</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>2025_0358</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-06-24</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-06-24</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>David Isaksson, Anders Forsberg</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>131106824</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Paljack, Mpd</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>600513</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6974597</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>2025_0353</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-06-24</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-06-24</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
         <is>
           <t>Kustpaketet</t>
         </is>

--- a/artfynd/A 25837-2025 artfynd.xlsx
+++ b/artfynd/A 25837-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AZ16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -797,6 +802,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131106814</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -927,6 +937,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131106821</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1052,6 +1067,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131106823</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1177,6 +1197,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131106827</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1297,6 +1322,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131106820</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1422,6 +1452,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131106818</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1547,6 +1582,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131106822</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1672,6 +1712,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131106826</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1797,6 +1842,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131106816</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1922,6 +1972,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131106812</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2047,6 +2102,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131106817</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2172,6 +2232,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131106813</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2297,6 +2362,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131106815</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2422,6 +2492,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131106819</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2547,8 +2622,30 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131106824</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>